--- a/AAII_Financials/Quarterly/NOK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NOK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>NOK</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5185100</v>
+        <v>5501000</v>
       </c>
       <c r="E8" s="3">
+        <v>5111300</v>
+      </c>
+      <c r="F8" s="3">
         <v>7191500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5664700</v>
       </c>
-      <c r="G8" s="3">
-        <v>5338800</v>
-      </c>
       <c r="H8" s="3">
-        <v>4744900</v>
+        <v>5217900</v>
       </c>
       <c r="I8" s="3">
+        <v>4647600</v>
+      </c>
+      <c r="J8" s="3">
         <v>6195300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4824900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4785200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4794500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5986500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4984100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5936700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6057100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8250500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6744600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6390400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5802600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6953400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5814200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5621200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5181600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6536000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5494600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5554900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5547300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8058600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6965300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6698400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6019300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8124200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6045300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5833700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5406600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7462400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6170900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6304500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>6312800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>7814100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>6920800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2826000</v>
+        <v>2971600</v>
       </c>
       <c r="E9" s="3">
+        <v>2762600</v>
+      </c>
+      <c r="F9" s="3">
         <v>3955600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3145600</v>
       </c>
-      <c r="G9" s="3">
-        <v>2957100</v>
-      </c>
       <c r="H9" s="3">
-        <v>2738900</v>
+        <v>2856100</v>
       </c>
       <c r="I9" s="3">
+        <v>2658900</v>
+      </c>
+      <c r="J9" s="3">
         <v>3269500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2603200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2644400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2371300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3308300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2951900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3551300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3697300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4721700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4037500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3821400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3449200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4206300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3449300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3314700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3216500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4109300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3442700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3366500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3539700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4892600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4553300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4269200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4129300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4858200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3809000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3791400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3424700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4553000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3719400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3795700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3817200</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>4664700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>4299700</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2359000</v>
+        <v>2529400</v>
       </c>
       <c r="E10" s="3">
+        <v>2348700</v>
+      </c>
+      <c r="F10" s="3">
         <v>3235900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2519100</v>
       </c>
-      <c r="G10" s="3">
-        <v>2381700</v>
-      </c>
       <c r="H10" s="3">
-        <v>2006100</v>
+        <v>2361700</v>
       </c>
       <c r="I10" s="3">
+        <v>1988800</v>
+      </c>
+      <c r="J10" s="3">
         <v>2925800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2221700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2140800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2423100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2678200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2032200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2385400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2359800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3528800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2707200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2569000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2353400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2747100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2364900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2306400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1965000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2426700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2051900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2188400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2007500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3166000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2412000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2429300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1890000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3266000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2236200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2042300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1981900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2909300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2451500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2508800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2495500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3149300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2621100</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1354800</v>
+        <v>1397200</v>
       </c>
       <c r="E12" s="3">
+        <v>1335200</v>
+      </c>
+      <c r="F12" s="3">
         <v>1525200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1345800</v>
       </c>
-      <c r="G12" s="3">
-        <v>1351700</v>
-      </c>
       <c r="H12" s="3">
-        <v>1211600</v>
+        <v>1330600</v>
       </c>
       <c r="I12" s="3">
+        <v>1194300</v>
+      </c>
+      <c r="J12" s="3">
         <v>1175100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1152100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1145400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1166300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1172800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1095500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1121200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1187500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1353500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1259000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1187100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1163100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1212000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1115700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1124700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1016700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1232800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>928900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1057100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1114400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1248000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1298500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1324600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1382800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1378100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1243800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1279200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1281400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1375600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1358700</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1362100</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1484900</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>1503700</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>1427400</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,53 +1496,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>212200</v>
+        <v>493500</v>
       </c>
       <c r="E14" s="3">
+        <v>220200</v>
+      </c>
+      <c r="F14" s="3">
         <v>240700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>109100</v>
       </c>
-      <c r="G14" s="3">
-        <v>103300</v>
-      </c>
       <c r="H14" s="3">
-        <v>129700</v>
+        <v>108000</v>
       </c>
       <c r="I14" s="3">
+        <v>124300</v>
+      </c>
+      <c r="J14" s="3">
         <v>37300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>217500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-117900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>127300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>136000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>101600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>62200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-38000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1583,8 +1603,8 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>10</v>
+      <c r="AK14" s="3">
+        <v>0</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>10</v>
@@ -1601,53 +1621,56 @@
       <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>241100</v>
+      </c>
+      <c r="E15" s="3">
         <v>241000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>81000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>335600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>334700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>285300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>22800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>267700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>287200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>281600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>73000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>282600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>296900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>289000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1705,8 +1728,8 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>10</v>
+      <c r="AK15" s="3">
+        <v>0</v>
       </c>
       <c r="AL15" s="3" t="s">
         <v>10</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ15" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4910600</v>
+        <v>5064500</v>
       </c>
       <c r="E17" s="3">
+        <v>4804600</v>
+      </c>
+      <c r="F17" s="3">
         <v>6254500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5271600</v>
       </c>
-      <c r="G17" s="3">
-        <v>5130900</v>
-      </c>
       <c r="H17" s="3">
-        <v>4652000</v>
+        <v>4930100</v>
       </c>
       <c r="I17" s="3">
+        <v>4529800</v>
+      </c>
+      <c r="J17" s="3">
         <v>5120600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4350900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4421900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4230200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5144200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4631700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5374500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5637800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7273600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6185900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5776700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5418500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6151200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5273600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5109100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4741600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6095100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5131400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5369500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5634200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7122400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6640700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6766700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6646100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7471200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6104000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6076300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5775500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6993400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6427900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6356100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>6463000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>7442000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>6855100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>274400</v>
+        <v>436400</v>
       </c>
       <c r="E18" s="3">
+        <v>306700</v>
+      </c>
+      <c r="F18" s="3">
         <v>936900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>393100</v>
       </c>
-      <c r="G18" s="3">
-        <v>207900</v>
-      </c>
       <c r="H18" s="3">
-        <v>93000</v>
+        <v>287700</v>
       </c>
       <c r="I18" s="3">
+        <v>117800</v>
+      </c>
+      <c r="J18" s="3">
         <v>1074600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>474000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>363200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>564200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>842300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>352500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>562200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>419400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>976900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>558700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>613700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>384100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>802200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>540600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>512100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>440000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>440900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>363300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>185500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-86900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>936300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>324600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-68200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-626800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>653000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-58700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-242700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-368900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>469000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-256900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-51600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-150200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>372100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>65700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,297 +2085,304 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1200</v>
+        <v>-141700</v>
       </c>
       <c r="E20" s="3">
+        <v>-145300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-36400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5900</v>
       </c>
-      <c r="G20" s="3">
-        <v>-16400</v>
-      </c>
       <c r="H20" s="3">
-        <v>37800</v>
+        <v>12900</v>
       </c>
       <c r="I20" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J20" s="3">
         <v>-40400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-11900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>117200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>17400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-25000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-106300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-52000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-60300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-71900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-60200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-76800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-61000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-117600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-211800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-70600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-84000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-64200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-123000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-105500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-69600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-319800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-181900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-70400</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>514200</v>
+        <v>819100</v>
       </c>
       <c r="E21" s="3">
+        <v>693000</v>
+      </c>
+      <c r="F21" s="3">
         <v>1054400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>734500</v>
       </c>
-      <c r="G21" s="3">
-        <v>559000</v>
-      </c>
       <c r="H21" s="3">
-        <v>340500</v>
+        <v>609500</v>
       </c>
       <c r="I21" s="3">
+        <v>397800</v>
+      </c>
+      <c r="J21" s="3">
         <v>1137800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>740600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>642900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>857700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>798100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>609700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>853700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>691000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1300300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>860200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>895500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>575100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1050500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>775400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>729000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>656400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>710100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>576000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>495300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>173900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1439400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>715400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>204700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-209300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1003100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>271400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>86700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-83400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>789900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>122300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>85300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>142000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>774700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>890900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3">
         <v>205500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>21100</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3">
         <v>337500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12300</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22" s="3">
         <v>280800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>40200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>55700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>207500</v>
+        <v>84500</v>
       </c>
       <c r="E23" s="3">
+        <v>231800</v>
+      </c>
+      <c r="F23" s="3">
         <v>704500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>268700</v>
       </c>
-      <c r="G23" s="3">
-        <v>144500</v>
-      </c>
       <c r="H23" s="3">
-        <v>-38900</v>
+        <v>166800</v>
       </c>
       <c r="I23" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="J23" s="3">
         <v>981500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>243100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>493900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>499500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>551600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>185200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>438900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>425900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>972500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>549000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>588700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>277800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>750200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>480300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>440100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>379700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>431900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>286500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>180000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-147900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>943300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>207000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-280000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-697400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>569000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-122900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-308500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-491900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>363500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-326500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-371400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-332200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>301700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-24700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>107200</v>
+        <v>53700</v>
       </c>
       <c r="E24" s="3">
+        <v>111800</v>
+      </c>
+      <c r="F24" s="3">
         <v>75100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>176000</v>
       </c>
-      <c r="G24" s="3">
-        <v>47000</v>
-      </c>
       <c r="H24" s="3">
-        <v>24900</v>
+        <v>50500</v>
       </c>
       <c r="I24" s="3">
+        <v>31300</v>
+      </c>
+      <c r="J24" s="3">
         <v>209100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>82500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>98600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>609000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>47600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>125500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>118400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2515400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>80500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>85700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>102300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>69800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>101100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3123900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>76800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>87300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-33900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>287200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>98000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-54100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-169900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>328800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>16600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-11000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-103200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>789900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-114400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>115600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>180800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-470700</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>130300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>100300</v>
+        <v>30800</v>
       </c>
       <c r="E26" s="3">
+        <v>119900</v>
+      </c>
+      <c r="F26" s="3">
         <v>629300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>92700</v>
       </c>
-      <c r="G26" s="3">
-        <v>97500</v>
-      </c>
       <c r="H26" s="3">
-        <v>-63800</v>
+        <v>116300</v>
       </c>
       <c r="I26" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="J26" s="3">
         <v>772300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>160600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>395400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>486600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-57500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>137600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>313300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>307500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3487800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>448500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>508100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>192000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>738300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>378000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>370300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>278700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2692000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>209700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>92700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-114000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>656100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>109000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-225900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-527500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>240100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-139600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-297600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-388700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-426400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-212100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-486900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-513000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>772400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-154900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>99200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>636400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>91500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>105700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-63800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>848900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>188500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-156400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>468200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-47500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>147100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>316600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>303100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3490000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>448500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>504900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>184500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>733900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>367200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>362900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>275600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2689000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>206500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>87300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-116300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>656100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>104100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-224700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-529900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>224800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-139600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-293200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-385400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-432000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-215400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-474600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-556400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>773500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-138500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,130 +3208,136 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-25100</v>
       </c>
       <c r="E29" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="F29" s="3">
         <v>10600</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
-        <v>15300</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="I29" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="J29" s="3">
         <v>69400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>34600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-548600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-14000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>21000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>3200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>2200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>6500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>3300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>11900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-7600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>45600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-1100</v>
-      </c>
-      <c r="V29" s="3">
-        <v>1100</v>
       </c>
       <c r="W29" s="3">
         <v>1100</v>
       </c>
       <c r="X29" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>4000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>15300</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>1200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>3500</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>53200</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>179000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>11200</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-15700</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-17600</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-30500</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1200</v>
+        <v>141700</v>
       </c>
       <c r="E32" s="3">
+        <v>145300</v>
+      </c>
+      <c r="F32" s="3">
         <v>36400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5900</v>
       </c>
-      <c r="G32" s="3">
-        <v>16400</v>
-      </c>
       <c r="H32" s="3">
-        <v>-37800</v>
+        <v>-12900</v>
       </c>
       <c r="I32" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="J32" s="3">
         <v>40400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>11900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-117200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-17400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>25000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>106300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>52000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>60300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>71900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>60200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>9000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>76800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>61000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>117600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>211800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>70600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>84000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>64200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>65900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>123000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>105500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>69600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>319800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>181900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>70400</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>90400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>99200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>636400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>91500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>105700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-63800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>848900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>188500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-156400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>468200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-47500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>147100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>316600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>303100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3493400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>460400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>497300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>230000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>732900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>368300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>364000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>266400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2685000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>200300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>102500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-133200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>657300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>101700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-228200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-533500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>228300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-86400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-292100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-206400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-434200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-204200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-490300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-574000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>743000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-145600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>99200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>636400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>91500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>105700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-63800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>848900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>188500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-156400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>468200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-47500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>147100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>316600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>303100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3493400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>460400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>497300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>230000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>732900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>368300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>364000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>266400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2685000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>200300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>102500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-133200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>657300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>101700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-228200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-533500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>228300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-86400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-292100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-206400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-434200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-204200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-490300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-574000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>743000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-145600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,1106 +4305,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4967400</v>
+      </c>
+      <c r="E41" s="3">
         <v>5708500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6413100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5739800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5633600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5991100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6856800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7855200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7342800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7078400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6890700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4874000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5574200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5244500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6055200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5615300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5937800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6880000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7253700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7433800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7672600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7467200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6922000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7095100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7732400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6954100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6899400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5783200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5520800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7012100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7406100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5315400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5482300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>7197400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8267900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6052000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>7457900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>8201400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>8800100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>8084000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>893400</v>
+      </c>
+      <c r="E42" s="3">
         <v>1013500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1154200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>907000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>886700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1268900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1748600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1911700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1996100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1981900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1756400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1797200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2030600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3138900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4092600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4697800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4392700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3432900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3158000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2966900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1779600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1750700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1331500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1084600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>660000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>491200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>304700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>645600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>449400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1027500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1011400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1180700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1221000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1725000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1361000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1670600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1883800</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>2412200</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>2494300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>3168100</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7809900</v>
+      </c>
+      <c r="E43" s="3">
         <v>7506100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7839600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6956500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6696400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7054700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6975900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5620100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6033400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6853000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7878900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8668500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8365700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8331200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7648000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7446000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6627600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6782300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7309000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6558300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6339500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5796100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7070600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5725100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6400400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7567200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8276900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8457300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8456000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8414100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8649400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8051100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>7932000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7637700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>8427300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>8383500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>8302700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>8669800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8946800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>8321100</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3133800</v>
+      </c>
+      <c r="E44" s="3">
         <v>2745300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2593600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2792400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2911300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2787500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2239400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2824000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2656200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2897800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3005400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3483300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3621200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3584300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3616300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3711100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3166400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2860100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2593200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2672900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2530700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2313100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2236200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2849000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3125500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3197600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3427500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4461400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4242100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4220200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3747400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3521100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3224800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3049100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2968800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3397400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>3309900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>3404000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2941600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>3131700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E45" s="3">
         <v>336700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>373400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>469300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>621300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>545800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>622200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1419800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1275000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>549100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>548200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>550400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>560000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>621500</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T45" s="3">
         <v>1212100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1169600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>931200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>939100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>931000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1182100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>607400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1323300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1262200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>689900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>713300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>984900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>945800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>887600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>792500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1047800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1045300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>960800</v>
-      </c>
-      <c r="AK45" s="3">
-        <v>1236400</v>
       </c>
       <c r="AL45" s="3">
         <v>1236400</v>
       </c>
       <c r="AM45" s="3">
+        <v>1236400</v>
+      </c>
+      <c r="AN45" s="3">
         <v>1028900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1143300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1085800</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1149200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16859400</v>
+      </c>
+      <c r="E46" s="3">
         <v>17310000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18541700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16865000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16749300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17648100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18622000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19630800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19303500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19360200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20079600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>19373400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20151700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20920300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22446600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22710900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21336600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>21125000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>21245100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>20570900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19253500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18509100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18167600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18077100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>19180400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18900000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>19621800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>20332400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>19614100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>21561500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>21606900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>19116100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>18905400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>20569900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>22261400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>20740000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>21983200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>23830700</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>24268500</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>23854200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2057600</v>
+      </c>
+      <c r="E47" s="3">
         <v>1973900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1830500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1909000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1933100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1851500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1707200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1783400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1747600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1827600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2103500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2131700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2005500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2041500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2188600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2299700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2035800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2018100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1437500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1363400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1390200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1433200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1280700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1308800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1413800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1510700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1576000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1607200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1528100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1549100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1428900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1336900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1251700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1224300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1300400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1376700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1472100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1658600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1655100</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1631600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2924700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2880200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2923600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2868700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2856100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2543200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2194800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2265200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2331500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3011100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3158000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3074700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3153900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3170400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3260800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3188100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3159800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3105300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3044200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2925900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2862900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2775600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2581300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2669500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2865800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3029400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3231400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3297700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3112800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3271600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2117400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1941600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1956600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1964300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2079000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2046500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2090300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2270100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2325300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2229100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8519400</v>
+      </c>
+      <c r="E49" s="3">
         <v>8610600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8682600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8815000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8913700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8791600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6768800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7021000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7031000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7159300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7284200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7158100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7343900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7413100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7675700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8085800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7905000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7640600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7644000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7598600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7446200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7277300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7008700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7838200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8613800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9248500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9287900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10234800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9841800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10366300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10415400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>9784500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9914900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>9789800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>10343600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>10761000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>11445400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>12895500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>12865000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>12616100</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8021200</v>
+      </c>
+      <c r="E52" s="3">
         <v>7993800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7887800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7644000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7590100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7758300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7512200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7454800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7267800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7207900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7152600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7084000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7705200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7975900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11992000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10038600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10051900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10080700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10046400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9551000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7838700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7624400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7058600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10382100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11093500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>12197700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11961300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12449600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11692200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11796900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>16172600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10500000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10400300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9928100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10044100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>10890000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>10784600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>11674700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>11591400</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>10691100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42586500</v>
+      </c>
+      <c r="E54" s="3">
         <v>42990900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>44143500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42290300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>42311200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42435100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40531100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42254100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>41636100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42804000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44058800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>42912800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>44483600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45603000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>47563700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>46323100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>44489100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>43969600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>43417100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>42009900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>38791600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>37619500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>36096900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>40275700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>43167300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>44886200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>45678400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>47921600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>45789000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>48546600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>46744700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>42679200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>42428900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>43476400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>46028500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>45814200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>47775500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>52329600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>52705200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>51022000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4011200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3636600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3496500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3592600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3498500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3280400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3326400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3103900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3108300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3280800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3783600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3784900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4647400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4544800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5238900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5075000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4269700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3975400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3988400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3479500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3299900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3172600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3165700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3287000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3550900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3584900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4419800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4728500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4580900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5001300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5646000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4459200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4282200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3935200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4483500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3973000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3977500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4244500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>4438200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3974500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>772300</v>
+      </c>
+      <c r="E58" s="3">
         <v>271000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1514600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1071200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1116900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2259000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1219600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1298200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1222500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>926700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>862200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>813900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>851500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>849600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>456300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>483100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>429800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>348300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>326300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>813100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>827400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>332800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>748100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>909200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1072400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1214900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>643200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>803600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>658800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1204600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2229800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2125500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1312100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>866300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>647400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>639500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>695600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>575200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>711300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>643200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6418400</v>
+      </c>
+      <c r="E59" s="3">
         <v>7141700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3963800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6745300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6864400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7427600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4693000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7308700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7144500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7521800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7438900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7198300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7063300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8111700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8453200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9251900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8670000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9083600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8804000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8536600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8069400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8056200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7816600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7607800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8129500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8958300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9010100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9648000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9361800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10235900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10576300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8254900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9001400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>9378000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9167800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>8443000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>9387700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>10104200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>9646400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>13842700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11201900</v>
+      </c>
+      <c r="E60" s="3">
         <v>11049200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11745900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11409100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11479700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12966900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11796300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11710900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11475400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11729400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12084700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11797200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12562200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13506100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14148500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14809900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13369500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13407300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13118700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12829100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12196600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11561600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11730400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11804000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12752700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13758100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>14073100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15180100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14601500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>16441800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16683600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>14839600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>13818300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>13418700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>14298600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>13055500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>14060800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>14923800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>14795900</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>14747700</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3065200</v>
+      </c>
+      <c r="E61" s="3">
         <v>3562800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3670300</v>
-      </c>
-      <c r="F61" s="3">
-        <v>3698200</v>
       </c>
       <c r="G61" s="3">
         <v>3698200</v>
       </c>
       <c r="H61" s="3">
+        <v>3698200</v>
+      </c>
+      <c r="I61" s="3">
         <v>3215500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3708500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3843400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3713700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4204300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4903300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4660200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4828600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4954400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5656500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5669400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5813700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5822100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5811900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5767900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5619000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5989000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5721100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6038500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6447300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5511100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5552200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5876300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5525600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5338600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3345200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3065800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3042600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3482900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3878700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3928100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>4013400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>4819700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>4292600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>4129500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1016800</v>
+      </c>
+      <c r="E62" s="3">
         <v>826700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>920500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>835400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>699900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>673400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>617000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>610100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>685700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>655900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>695300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>681600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>738000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>731200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4027200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4449200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4603800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5120100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5556000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5760300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5807400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6011500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6133000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6636300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7255600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7546900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8073800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9188600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8748900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>8795700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>8597300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>8116500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9000300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9144100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>9654700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>10252700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>9492000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>8774200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>8996100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>9300100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18261200</v>
+      </c>
+      <c r="E66" s="3">
         <v>18463000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19418800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19208000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19042900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19933000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19051700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19441200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19116000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19896400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21257900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20314400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21256600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22379400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>23935200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25049500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>23907700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>24468900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>24597100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>24465000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>23717200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23648900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23664300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>24565000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>26540700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26905300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>27787900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>30341800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>28968900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>30678900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>28659300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>26097300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>25938100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>26133500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>27921800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>27320500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>28528800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>29592900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>29118700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>29195000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1773100</v>
+      </c>
+      <c r="E72" s="3">
         <v>2046600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2180300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1733000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1888400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1870900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2025100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1460000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1398300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1807100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1551900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1740100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1824200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1671000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18676400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15253000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14990800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2524800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2750400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3446100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3746400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3964800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-4132200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1507000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1793500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1955600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1883000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2663100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2338700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-1800300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1256200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-1387800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-1289100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>168000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1286900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1729000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1887200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3637600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4211600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3462700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24214600</v>
+      </c>
+      <c r="E76" s="3">
         <v>24421800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24617800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22975500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23160300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22406000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21386300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22701300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22419400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22805000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22700300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22507400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23122300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23115000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23628400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21273600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20581400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19500700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18820000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17544900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15074400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13970700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12432600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15710700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16626600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17980900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17890600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17579800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>16820200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17867600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18085400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>16581900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>16490900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>17342900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>18106700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>18493800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>19246600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>22736700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>23586500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>21827000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>99200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>636400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>91500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>105700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-63800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>848900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>188500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-156400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>468200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-47500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>147100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>316600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>303100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3493400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>460400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>497300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>230000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>732900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>368300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>364000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>266400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2685000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>200300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>102500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-133200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>657300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>101700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-228200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-533500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>228300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-86400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-292100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-206400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-434200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-204200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-490300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-574000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>743000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-145600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>334700</v>
+      </c>
+      <c r="E83" s="3">
         <v>285300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>253600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>267700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>203600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>198500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>311700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>193700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>204100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>195600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>145300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>178500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>190300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>193300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>327800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>311200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>306800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>297300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>300300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>295100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>288800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>276600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>278300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>289600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>315300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>321800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>496100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>508400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>484700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>488000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>434100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>394300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>395300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>408500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>426400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>448800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>456600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>474200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>473000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>439000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>902800</v>
+        <v>-708300</v>
       </c>
       <c r="E89" s="3">
+        <v>901600</v>
+      </c>
+      <c r="F89" s="3">
         <v>440300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>700500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>245400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>962000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>215300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>812000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>523900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1151100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2067000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-320700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-363500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>90200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>628000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>422600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-46800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>606500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>526900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>785100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>112100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1331100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>876700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>428700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>363300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>151300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1855000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>568400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1077600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-893600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1639500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-90800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-915700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-120800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2231600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-834800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1165700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-555200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>599800</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>274700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-147400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-177600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-173800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-197100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-142100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-182700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-163600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-119300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-101800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-120800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-164700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-152400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-138600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-252100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-195000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-116000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-101000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-189000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-159000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-129000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-119600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-162300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-138600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-97100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-173900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-225300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-234000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-154100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-209300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-202300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-151700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-114200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-285500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-171700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-175000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-159300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-176100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-145600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>318700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-56500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-382800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-221800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-291300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-684200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-220500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-92600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>298900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-107900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>102800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>117500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1163800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-246600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>75300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-495000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-684400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-934200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-252600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1111400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-27500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-514500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-430900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-511700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-334900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-321800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-260300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-211900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>351700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-83700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>121800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-106300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>375500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-729100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>152600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-49400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>145900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-248800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>568100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-214800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E96" s="3">
         <v>193700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>190200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>253400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>252500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>174000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>167700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>185100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>241100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>179100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>183500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>181000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>182300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>121700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-137300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-123200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-5400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-128700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-393200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-291700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-145100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1026600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-16500</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-142500</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-945800</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-1200</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-1777100</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-322200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1464300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>603500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-346100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-664700</v>
       </c>
-      <c r="H100" s="3">
-        <v>-1364000</v>
-      </c>
       <c r="I100" s="3">
+        <v>-1365100</v>
+      </c>
+      <c r="J100" s="3">
         <v>-527000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-445000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-489700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-688300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-322800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-353500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-449800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-504100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-269100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-255000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-290500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-98700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-552900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-85100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-142800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-498200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-296200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-149500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1015600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>443700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-138900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-369900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-577600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>518000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>98200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-66500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1091400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-180600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-478000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1503500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>208900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-599800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1876900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-165600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-81100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>68300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-63600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-46400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>26500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-45900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-34800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-129300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>41200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>57500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>47800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-134000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>45400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>59800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>46700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>48800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>35500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-8500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>64300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-45900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-30500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>7900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-67700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>47800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-71800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-17900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-130100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>48700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-83400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-46100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>12300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-43800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-189600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>147900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-589200</v>
+        <v>-688900</v>
       </c>
       <c r="E102" s="3">
+        <v>-590300</v>
+      </c>
+      <c r="F102" s="3">
         <v>669200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>112600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-876100</v>
       </c>
-      <c r="H102" s="3">
-        <v>-1167300</v>
-      </c>
       <c r="I102" s="3">
+        <v>-1168400</v>
+      </c>
+      <c r="J102" s="3">
         <v>-463800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>210800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>342900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>352800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1800600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-530300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>304600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-695300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>300200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-282100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-961900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-379800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-229800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-375800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-66700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>382800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>103700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-261600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1013500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>281100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1388100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>34300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1375200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-477300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1729400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-214900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1715100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-893800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>2215900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1405900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-381500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-598600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>716000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1833500</v>
       </c>
     </row>
